--- a/templates/partner.xlsx
+++ b/templates/partner.xlsx
@@ -579,17 +579,17 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="23" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="11" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="15" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="48" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="42" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="9" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="11" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="13" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="27" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="28" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="6" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="8" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="13" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="8" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="8" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="13" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="42" customHeight="1">
